--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.61212535127826</v>
+        <v>4.974470369582717</v>
       </c>
       <c r="D2" t="n">
-        <v>30.90951737654281</v>
+        <v>5.022796573688206</v>
       </c>
       <c r="E2" t="n">
-        <v>14.03916763293507</v>
+        <v>2.281364740351949</v>
       </c>
       <c r="F2" t="n">
-        <v>19.92533159694522</v>
+        <v>3.237866384503598</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.47908218722704</v>
+        <v>10.64035085542439</v>
       </c>
       <c r="D3" t="n">
-        <v>81.01101950713996</v>
+        <v>13.16429066991024</v>
       </c>
       <c r="E3" t="n">
-        <v>14.03916763293507</v>
+        <v>2.281364740351949</v>
       </c>
       <c r="F3" t="n">
-        <v>19.92533159694522</v>
+        <v>3.237866384503598</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.38708709064394</v>
+        <v>6.56290165222964</v>
       </c>
       <c r="D4" t="n">
-        <v>39.75089915445051</v>
+        <v>6.459521112598208</v>
       </c>
       <c r="E4" t="n">
-        <v>14.03916763293507</v>
+        <v>2.281364740351949</v>
       </c>
       <c r="F4" t="n">
-        <v>19.92533159694522</v>
+        <v>3.237866384503598</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.42690331508901</v>
+        <v>4.456871788701965</v>
       </c>
       <c r="D5" t="n">
-        <v>24.08318915758459</v>
+        <v>3.913518238107496</v>
       </c>
       <c r="E5" t="n">
-        <v>14.03916763293507</v>
+        <v>2.281364740351949</v>
       </c>
       <c r="F5" t="n">
-        <v>19.92533159694522</v>
+        <v>3.237866384503598</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.80192681700057</v>
+        <v>8.417813107762592</v>
       </c>
       <c r="D6" t="n">
-        <v>49.98004852657728</v>
+        <v>8.121757885568808</v>
       </c>
       <c r="E6" t="n">
-        <v>14.03916763293507</v>
+        <v>2.281364740351949</v>
       </c>
       <c r="F6" t="n">
-        <v>19.92533159694522</v>
+        <v>3.237866384503598</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
